--- a/rules/CORE-000616/negative/01/data/unit-test-coreid-FB4403-negative.xlsx
+++ b/rules/CORE-000616/negative/01/data/unit-test-coreid-FB4403-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\core-contributor\rules\CORE-000616\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54279FA-F4BE-490D-BF5B-ED2998784C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263D8398-8668-43E3-80FF-A908D973F407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -1009,7 +1009,7 @@
         <v>136</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
         <v>47</v>
@@ -1708,6 +1708,7 @@
       <c r="AE6" t="s">
         <v>103</v>
       </c>
+      <c r="AF6" s="11"/>
     </row>
     <row r="7" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
@@ -1855,6 +1856,7 @@
       <c r="AE8" t="s">
         <v>103</v>
       </c>
+      <c r="AF8" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/CORE-000616/negative/01/data/unit-test-coreid-FB4403-negative.xlsx
+++ b/rules/CORE-000616/negative/01/data/unit-test-coreid-FB4403-negative.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\core-contributor\rules\CORE-000616\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263D8398-8668-43E3-80FF-A908D973F407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8E9FA1-6E74-4BED-A056-451B0D2D7C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="141">
   <si>
     <t>Product</t>
   </si>
@@ -955,7 +955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1063,7 +1063,7 @@
         <v>136</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
         <v>140</v>
@@ -1103,7 +1103,7 @@
         <v>136</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
         <v>140</v>
@@ -1129,6 +1129,86 @@
         <v>125</v>
       </c>
       <c r="F9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1994,7 +2074,7 @@
       <c r="G5" t="s">
         <v>132</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2034,7 +2114,7 @@
       <c r="G7" t="s">
         <v>134</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="11" t="s">
         <v>102</v>
       </c>
     </row>
